--- a/mosip_master/xlsx/loc_hierarchy_list.xlsx
+++ b/mosip_master/xlsx/loc_hierarchy_list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>lang_code</t>
   </si>
@@ -50,60 +50,6 @@
     <t>Country</t>
   </si>
   <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>دولة</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>Pays</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>المناطق</t>
-  </si>
-  <si>
-    <t>Région</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
-    <t>المحافظة</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>مدينة</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>منطقة</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>رمز بريدي</t>
-  </si>
-  <si>
-    <t>code postal</t>
-  </si>
-  <si>
     <t>Districts</t>
   </si>
   <si>
@@ -114,6 +60,9 @@
   </si>
   <si>
     <t>Villages</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
   </si>
 </sst>
 </file>
@@ -785,7 +734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -794,8 +743,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1338,8 +1285,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="21.2761904761905" customWidth="1"/>
@@ -1371,334 +1318,82 @@
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
+      <c r="D2" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>6</v>
+      </c>
+      <c r="D3" s="5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="b">
         <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" s="5">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5" t="b">
         <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4">
-        <v>2</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4">
-        <v>3</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4">
-        <v>3</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4">
-        <v>3</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="4">
-        <v>4</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="4">
-        <v>4</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="4">
-        <v>4</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="4">
+      <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="4">
-        <v>5</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="4">
-        <v>5</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" spans="1:4">
-      <c r="A20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="6">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" spans="1:4">
-      <c r="A21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="7">
-        <v>1</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" spans="1:4">
-      <c r="A22" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="8">
-        <v>2</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" spans="1:4">
-      <c r="A23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="8">
-        <v>3</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" spans="1:4">
-      <c r="A24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="7">
-        <v>4</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" spans="1:4">
-      <c r="A25" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="7">
-        <v>5</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="7" t="b">
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="5" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D20" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D7" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
